--- a/outputs/daily/hr_rankings_2026-07-02.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-02.xlsx
@@ -7691,24 +7691,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>668804</t>
+          <t>607208</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bryan Reynolds</t>
+          <t>Trea Turner</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>PIT</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>2026-07-02T16:35:00Z</t>
@@ -7721,17 +7721,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Alan Rangel</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>660604</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>54.5</v>
+        <v>54.6</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7754,26 +7754,26 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Good Environment, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>46</v>
+        <v>26.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>27.2</v>
+        <v>49.3</v>
       </c>
       <c r="R27" t="n">
         <v>80.8</v>
       </c>
       <c r="S27" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T27" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U27" t="n">
-        <v>8.800000000000001</v>
+        <v>87</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -7808,7 +7808,7 @@
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr"/>
@@ -7825,127 +7825,127 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>40.42</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>91.34</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>102.1504</t>
+          <t>99.3035</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>0.4498</t>
+          <t>0.3743</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t>0.1253</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>0.2965</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>72.76</t>
+          <t>71.48</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>18.57</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>33.84</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.1362</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>0.3892</t>
+          <t>0.457</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>0.1569</t>
+          <t>0.198</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
@@ -7971,24 +7971,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>607208</t>
+          <t>668804</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Trea Turner</t>
+          <t>Bryan Reynolds</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>2026-07-02T16:35:00Z</t>
@@ -8001,17 +8001,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Alan Rangel</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>660604</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -8034,26 +8034,26 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>26.6</v>
+        <v>46</v>
       </c>
       <c r="Q28" t="n">
-        <v>49.3</v>
+        <v>27.2</v>
       </c>
       <c r="R28" t="n">
         <v>80.8</v>
       </c>
       <c r="S28" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T28" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U28" t="n">
-        <v>83.59999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -8088,7 +8088,7 @@
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr"/>
@@ -8105,127 +8105,127 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 5/28, 0 HR</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 5.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>91.34</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>99.3035</t>
+          <t>102.1504</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>0.3743</t>
+          <t>0.4498</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>0.1253</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>0.2965</t>
+          <t>0.359</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>71.48</t>
+          <t>72.76</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>18.57</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>33.84</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.1362</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>0.3892</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>0.1569</t>
         </is>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
@@ -24396,7 +24396,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>80</v>
       </c>
       <c r="U87" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -24496,7 +24496,7 @@
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-07-02.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-02.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>74</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>80</v>
       </c>
       <c r="U2" t="n">
-        <v>31.6</v>
+        <v>30.3</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 1 HR</t>
+          <t>Last 7 games: 5/25, 1 HR</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -6027,47 +6027,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>650489</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Willi Castro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-02T18:10:00Z</t>
+          <t>2026-07-02T19:10:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Chase Burns</t>
+          <t>Ryan Gusto</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>695505</t>
+          <t>687473</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>55.6</v>
+        <v>55.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6090,26 +6090,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>53.4</v>
+        <v>28.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>37.9</v>
+        <v>50.8</v>
       </c>
       <c r="R21" t="n">
-        <v>47.6</v>
+        <v>81.7</v>
       </c>
       <c r="S21" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U21" t="n">
-        <v>65.2</v>
+        <v>34.2</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -6161,27 +6161,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/31, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.8% barrel, 6.5 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -6191,112 +6191,112 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>45.66</t>
+          <t>40.31</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>91.47</t>
+          <t>87.96</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>102.3936</t>
+          <t>100.1044</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.3687</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.2077</t>
+          <t>0.1316</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3308</t>
+          <t>0.3039</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>74.67</t>
+          <t>72.51</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.2224</t>
+          <t>0.1253</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>38.91</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>89.22</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.3511</t>
+          <t>0.4446</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.1711</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
@@ -6307,47 +6307,47 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>650489</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Willi Castro</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-02T19:10:00Z</t>
+          <t>2026-07-02T23:40:00Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Ryan Gusto</t>
+          <t>Stephen Kolek</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>687473</t>
+          <t>663568</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -6370,58 +6370,62 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>28.3</v>
+        <v>65</v>
       </c>
       <c r="Q22" t="n">
-        <v>50.8</v>
+        <v>34.2</v>
       </c>
       <c r="R22" t="n">
-        <v>81.7</v>
+        <v>23.2</v>
       </c>
       <c r="S22" t="n">
-        <v>94.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U22" t="n">
-        <v>34.2</v>
+        <v>100</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6441,142 +6445,134 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/31, 1 HR</t>
+          <t>Hot streak: 8 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.8% barrel, 6.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 8.3 HR allowed</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>40.31</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>87.96</t>
+          <t>93.17</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>100.1044</t>
+          <t>105.5339</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.3687</t>
+          <t>0.5101</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.1316</t>
+          <t>0.2383</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.3039</t>
+          <t>0.3677</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>72.51</t>
+          <t>79.55</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>24.81</t>
+          <t>86.84</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>45.38</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.1253</t>
+          <t>0.2689</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0.4446</t>
+          <t>0.3899</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0.1711</t>
+          <t>0.1278</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>26.75</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>Out To LF</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>21.88</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr"/>
@@ -6587,47 +6583,47 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-02T23:40:00Z</t>
+          <t>2026-07-02T18:10:00Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Stephen Kolek</t>
+          <t>Chase Burns</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>663568</t>
+          <t>695505</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -6636,7 +6632,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>55.5</v>
+        <v>55.4</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6650,62 +6646,58 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>65</v>
+        <v>53.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>34.2</v>
+        <v>37.9</v>
       </c>
       <c r="R23" t="n">
-        <v>23.2</v>
+        <v>47.6</v>
       </c>
       <c r="S23" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T23" t="n">
         <v>50</v>
       </c>
       <c r="U23" t="n">
-        <v>100</v>
+        <v>60.7</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6725,134 +6717,142 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Hot streak: 8 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 8.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.2 HR allowed</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>45.66</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>93.17</t>
+          <t>91.47</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>105.5339</t>
+          <t>102.3936</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.5101</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0.2383</t>
+          <t>0.2077</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.3677</t>
+          <t>0.3308</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>79.55</t>
+          <t>74.67</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>86.84</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>45.38</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>0.2689</t>
+          <t>0.2224</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>38.91</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0.3899</t>
+          <t>0.3511</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0.1278</t>
+          <t>0.1439</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>21.88</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr"/>
-      <c r="BH23" t="inlineStr"/>
+          <t>27.82</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>In From RF</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr"/>
@@ -19643,32 +19643,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>687263</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-03T01:40:00Z</t>
+          <t>2026-07-02T18:10:00Z</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -19678,12 +19678,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Bryce Miller</t>
+          <t>Chase Burns</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>682243</t>
+          <t>695505</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -19692,7 +19692,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>47.9</v>
+        <v>48.1</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -19706,62 +19706,58 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>50.8</v>
+        <v>33.4</v>
       </c>
       <c r="Q70" t="n">
-        <v>35.9</v>
+        <v>37.9</v>
       </c>
       <c r="R70" t="n">
-        <v>25.4</v>
+        <v>47.6</v>
       </c>
       <c r="S70" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T70" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U70" t="n">
-        <v>36.3</v>
+        <v>12</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19781,134 +19777,142 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 4/20, 0 HR</t>
         </is>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 9.2 HR allowed</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>100.1597</t>
+          <t>100.7774</t>
         </is>
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>0.4362</t>
+          <t>0.3844</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>0.2202</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr">
         <is>
-          <t>0.3223</t>
+          <t>0.3041</t>
         </is>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>70.98</t>
+          <t>73.19</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>11.55</t>
+          <t>32.94</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>36.69</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>0.2233</t>
+          <t>0.1516</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>34.11</t>
+          <t>38.91</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>87.92</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="BD70" t="inlineStr">
         <is>
-          <t>0.3755</t>
+          <t>0.3511</t>
         </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.1439</t>
         </is>
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>30.6</t>
-        </is>
-      </c>
-      <c r="BG70" t="inlineStr"/>
-      <c r="BH70" t="inlineStr"/>
+          <t>27.82</t>
+        </is>
+      </c>
+      <c r="BG70" t="inlineStr">
+        <is>
+          <t>In From RF</t>
+        </is>
+      </c>
+      <c r="BH70" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
       <c r="BI70" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ70" t="inlineStr"/>
@@ -19919,32 +19923,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>687263</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-02T18:10:00Z</t>
+          <t>2026-07-03T01:40:00Z</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -19954,12 +19958,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Chase Burns</t>
+          <t>Bryce Miller</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>695505</t>
+          <t>682243</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -19968,7 +19972,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -19982,58 +19986,62 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>33.4</v>
+        <v>50.8</v>
       </c>
       <c r="Q71" t="n">
-        <v>37.9</v>
+        <v>35.9</v>
       </c>
       <c r="R71" t="n">
-        <v>47.6</v>
+        <v>25.4</v>
       </c>
       <c r="S71" t="n">
-        <v>93.2</v>
+        <v>88.7</v>
       </c>
       <c r="T71" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U71" t="n">
-        <v>7</v>
+        <v>36.3</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC71" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -20053,142 +20061,134 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 9.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>89.22</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>100.7774</t>
+          <t>100.1597</t>
         </is>
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>0.3844</t>
+          <t>0.4362</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.2202</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr">
         <is>
-          <t>0.3041</t>
+          <t>0.3223</t>
         </is>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>73.19</t>
+          <t>70.98</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>32.94</t>
+          <t>11.55</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>0.1516</t>
+          <t>0.2233</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>38.91</t>
+          <t>34.11</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>89.22</t>
+          <t>87.92</t>
         </is>
       </c>
       <c r="BD71" t="inlineStr">
         <is>
-          <t>0.3511</t>
+          <t>0.3755</t>
         </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>27.82</t>
-        </is>
-      </c>
-      <c r="BG71" t="inlineStr">
-        <is>
-          <t>In From RF</t>
-        </is>
-      </c>
-      <c r="BH71" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
+          <t>30.6</t>
+        </is>
+      </c>
+      <c r="BG71" t="inlineStr"/>
+      <c r="BH71" t="inlineStr"/>
       <c r="BI71" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ71" t="inlineStr"/>
@@ -26283,47 +26283,47 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-02T23:15:00Z</t>
+          <t>2026-07-02T18:10:00Z</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -26346,62 +26346,58 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>48.5</v>
+        <v>40.1</v>
       </c>
       <c r="Q94" t="n">
-        <v>43.2</v>
+        <v>14.1</v>
       </c>
       <c r="R94" t="n">
-        <v>30.9</v>
+        <v>47.6</v>
       </c>
       <c r="S94" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T94" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U94" t="n">
-        <v>0</v>
+        <v>16.6</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr"/>
       <c r="AC94" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -26421,12 +26417,12 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
@@ -26436,12 +26432,12 @@
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/25, 0 HR</t>
+          <t>Last 7 games: 3/13, 0 HR</t>
         </is>
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.8% barrel, 11.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.2% barrel, 5.9 HR allowed</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
@@ -26451,104 +26447,112 @@
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>45.51</t>
+          <t>40.66</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>91.25</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
         <is>
-          <t>102.356</t>
+          <t>100.9038</t>
         </is>
       </c>
       <c r="AR94" t="inlineStr">
         <is>
-          <t>0.4013</t>
+          <t>0.4381</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>0.1837</t>
+          <t>0.1828</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr">
         <is>
-          <t>0.3027</t>
+          <t>0.3408</t>
         </is>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>75.69</t>
+          <t>73.96</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>58.12</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.42</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>24.87</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>0.1379</t>
+          <t>0.1999</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>34.49</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="BD94" t="inlineStr">
         <is>
-          <t>0.3999</t>
+          <t>0.274</t>
         </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
-          <t>0.1539</t>
+          <t>0.0912</t>
         </is>
       </c>
       <c r="BF94" t="inlineStr">
         <is>
-          <t>24.1</t>
-        </is>
-      </c>
-      <c r="BG94" t="inlineStr"/>
-      <c r="BH94" t="inlineStr"/>
+          <t>23.82</t>
+        </is>
+      </c>
+      <c r="BG94" t="inlineStr">
+        <is>
+          <t>In From RF</t>
+        </is>
+      </c>
+      <c r="BH94" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
       <c r="BI94" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ94" t="inlineStr"/>
@@ -26559,47 +26563,47 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-02T18:10:00Z</t>
+          <t>2026-07-02T23:15:00Z</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -26608,7 +26612,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>43.6</v>
+        <v>43.9</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -26622,58 +26626,62 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>40.1</v>
+        <v>48.5</v>
       </c>
       <c r="Q95" t="n">
-        <v>14.1</v>
+        <v>43.2</v>
       </c>
       <c r="R95" t="n">
-        <v>47.6</v>
+        <v>30.9</v>
       </c>
       <c r="S95" t="n">
-        <v>86.40000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T95" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U95" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W95" t="inlineStr">
+      <c r="Z95" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC95" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -26693,12 +26701,12 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
@@ -26708,12 +26716,12 @@
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/15, 0 HR</t>
+          <t>Last 7 games: 2/25, 0 HR</t>
         </is>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.2% barrel, 5.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.8% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
@@ -26723,112 +26731,104 @@
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>40.66</t>
+          <t>45.51</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>91.25</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>100.9038</t>
+          <t>102.356</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>0.4381</t>
+          <t>0.4013</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>0.1828</t>
+          <t>0.1837</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr">
         <is>
-          <t>0.3408</t>
+          <t>0.3027</t>
         </is>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>73.96</t>
+          <t>75.69</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>58.12</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>0.1999</t>
+          <t>0.1379</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>34.49</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD95" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>0.3999</t>
         </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
-          <t>0.0912</t>
+          <t>0.1539</t>
         </is>
       </c>
       <c r="BF95" t="inlineStr">
         <is>
-          <t>23.82</t>
-        </is>
-      </c>
-      <c r="BG95" t="inlineStr">
-        <is>
-          <t>In From RF</t>
-        </is>
-      </c>
-      <c r="BH95" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="BG95" t="inlineStr"/>
+      <c r="BH95" t="inlineStr"/>
       <c r="BI95" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ95" t="inlineStr"/>
@@ -30163,27 +30163,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>553993</t>
+          <t>693304</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Eugenio Suárez</t>
+          <t>Nick Gonzales</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-02T18:10:00Z</t>
+          <t>2026-07-02T16:35:00Z</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -30193,17 +30193,17 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Alan Rangel</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>660604</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -30212,7 +30212,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
@@ -30226,26 +30226,26 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P108" t="n">
-        <v>32</v>
+        <v>15.7</v>
       </c>
       <c r="Q108" t="n">
-        <v>14.1</v>
+        <v>27.3</v>
       </c>
       <c r="R108" t="n">
-        <v>47.6</v>
+        <v>80.8</v>
       </c>
       <c r="S108" t="n">
-        <v>94.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T108" t="n">
         <v>50</v>
       </c>
       <c r="U108" t="n">
-        <v>36</v>
+        <v>34.5</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
@@ -30297,142 +30297,142 @@
       </c>
       <c r="AH108" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Contact streak: 7/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL108" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.2% barrel, 5.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>88.03</t>
+          <t>86.63</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
         <is>
-          <t>99.1722</t>
+          <t>98.4206</t>
         </is>
       </c>
       <c r="AR108" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>0.3806</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.1056</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr">
         <is>
-          <t>0.2773</t>
+          <t>0.3141</t>
         </is>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>40.72</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>20.56</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t>0.0817</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>34.49</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="BD108" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>0.3892</t>
         </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
-          <t>0.0912</t>
+          <t>0.1569</t>
         </is>
       </c>
       <c r="BF108" t="inlineStr">
         <is>
-          <t>23.82</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="BG108" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>98</t>
         </is>
       </c>
       <c r="BI108" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ108" t="inlineStr"/>
@@ -30443,47 +30443,47 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>553993</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Eugenio Suárez</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-02T22:40:00Z</t>
+          <t>2026-07-02T18:10:00Z</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -30506,65 +30506,61 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>21.9</v>
+        <v>32</v>
       </c>
       <c r="Q109" t="n">
-        <v>40.7</v>
+        <v>14.1</v>
       </c>
       <c r="R109" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S109" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T109" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U109" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W109" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr"/>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD109" t="inlineStr"/>
@@ -30581,27 +30577,27 @@
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/29, 0 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL109" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 10.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.2% barrel, 5.9 HR allowed</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
@@ -30611,104 +30607,112 @@
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.03</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>98.6732</t>
+          <t>99.1722</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>0.358</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>0.2773</t>
         </is>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>47.61</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.2063</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>34.49</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="BD109" t="inlineStr">
         <is>
-          <t>0.4076</t>
+          <t>0.274</t>
         </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
-          <t>0.1468</t>
+          <t>0.0912</t>
         </is>
       </c>
       <c r="BF109" t="inlineStr">
         <is>
-          <t>22.01</t>
-        </is>
-      </c>
-      <c r="BG109" t="inlineStr"/>
-      <c r="BH109" t="inlineStr"/>
+          <t>23.82</t>
+        </is>
+      </c>
+      <c r="BG109" t="inlineStr">
+        <is>
+          <t>In From RF</t>
+        </is>
+      </c>
+      <c r="BH109" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
       <c r="BI109" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ109" t="inlineStr"/>
@@ -30719,47 +30723,47 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>693304</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Nick Gonzales</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-02T16:35:00Z</t>
+          <t>2026-07-02T22:40:00Z</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Alan Rangel</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>660604</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -30768,7 +30772,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>40.5</v>
+        <v>40.7</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
@@ -30782,61 +30786,65 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Good Environment</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P110" t="n">
-        <v>15.7</v>
+        <v>21.9</v>
       </c>
       <c r="Q110" t="n">
-        <v>27.3</v>
+        <v>40.7</v>
       </c>
       <c r="R110" t="n">
-        <v>80.8</v>
+        <v>27.6</v>
       </c>
       <c r="S110" t="n">
-        <v>76.2</v>
+        <v>88.7</v>
       </c>
       <c r="T110" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U110" t="n">
-        <v>29.4</v>
+        <v>0</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W110" t="inlineStr">
+      <c r="Z110" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD110" t="inlineStr"/>
@@ -30853,12 +30861,12 @@
       </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -30868,127 +30876,119 @@
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/19, 0 HR</t>
+          <t>Last 7 games: 2/29, 0 HR</t>
         </is>
       </c>
       <c r="AL110" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 10.2 HR allowed</t>
         </is>
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>86.63</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>98.4206</t>
+          <t>98.6732</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
         <is>
-          <t>0.3806</t>
+          <t>0.359</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
         <is>
-          <t>0.1056</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr">
         <is>
-          <t>0.3141</t>
+          <t>0.306</t>
         </is>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>40.72</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>0.0817</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BD110" t="inlineStr">
         <is>
-          <t>0.3892</t>
+          <t>0.4076</t>
         </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
-          <t>0.1569</t>
+          <t>0.1468</t>
         </is>
       </c>
       <c r="BF110" t="inlineStr">
         <is>
-          <t>30.41</t>
-        </is>
-      </c>
-      <c r="BG110" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH110" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
+          <t>22.01</t>
+        </is>
+      </c>
+      <c r="BG110" t="inlineStr"/>
+      <c r="BH110" t="inlineStr"/>
       <c r="BI110" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ110" t="inlineStr"/>
@@ -45035,47 +45035,47 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>624431</t>
+          <t>691026</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Jose Trevino</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-07-02T18:10:00Z</t>
+          <t>2026-07-02T23:15:00Z</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Hurston Waldrep</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>694462</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -45098,58 +45098,62 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P162" t="n">
-        <v>9</v>
+        <v>12.9</v>
       </c>
       <c r="Q162" t="n">
-        <v>14.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R162" t="n">
-        <v>47.6</v>
+        <v>30.9</v>
       </c>
       <c r="S162" t="n">
-        <v>52.4</v>
+        <v>71.7</v>
       </c>
       <c r="T162" t="n">
         <v>50</v>
       </c>
       <c r="U162" t="n">
-        <v>21.1</v>
+        <v>13.3</v>
       </c>
       <c r="V162" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W162" t="inlineStr">
+      <c r="Z162" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC162" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -45169,12 +45173,12 @@
       </c>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
@@ -45184,12 +45188,12 @@
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL162" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.2% barrel, 5.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.3% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM162" t="inlineStr">
@@ -45199,112 +45203,104 @@
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>32.02</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>86.22</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>97.186</t>
+          <t>98.2909</t>
         </is>
       </c>
       <c r="AR162" t="inlineStr">
         <is>
-          <t>0.3284</t>
+          <t>0.3337</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>0.0885</t>
+          <t>0.0818</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr">
         <is>
-          <t>0.2584</t>
+          <t>0.2972</t>
         </is>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>69.18</t>
+          <t>70.75</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>32.18</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>0.0612</t>
+          <t>0.0939</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>34.49</t>
+          <t>40.09</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>85.32</t>
         </is>
       </c>
       <c r="BD162" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>0.2785</t>
         </is>
       </c>
       <c r="BE162" t="inlineStr">
         <is>
-          <t>0.0912</t>
+          <t>0.0436</t>
         </is>
       </c>
       <c r="BF162" t="inlineStr">
         <is>
-          <t>23.82</t>
-        </is>
-      </c>
-      <c r="BG162" t="inlineStr">
-        <is>
-          <t>In From RF</t>
-        </is>
-      </c>
-      <c r="BH162" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
+          <t>6.45</t>
+        </is>
+      </c>
+      <c r="BG162" t="inlineStr"/>
+      <c r="BH162" t="inlineStr"/>
       <c r="BI162" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ162" t="inlineStr"/>
@@ -45315,47 +45311,47 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>691026</t>
+          <t>624431</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Jose Trevino</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-07-02T23:15:00Z</t>
+          <t>2026-07-02T18:10:00Z</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Hurston Waldrep</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>694462</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -45364,7 +45360,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
@@ -45378,62 +45374,58 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P163" t="n">
-        <v>12.9</v>
+        <v>9</v>
       </c>
       <c r="Q163" t="n">
-        <v>9.699999999999999</v>
+        <v>14.1</v>
       </c>
       <c r="R163" t="n">
-        <v>30.9</v>
+        <v>47.6</v>
       </c>
       <c r="S163" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T163" t="n">
         <v>50</v>
       </c>
       <c r="U163" t="n">
-        <v>13.3</v>
+        <v>19.5</v>
       </c>
       <c r="V163" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W163" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X163" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y163" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr"/>
       <c r="AC163" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -45458,7 +45450,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ163" t="inlineStr">
@@ -45468,12 +45460,12 @@
       </c>
       <c r="AK163" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL163" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.3% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.2% barrel, 5.9 HR allowed</t>
         </is>
       </c>
       <c r="AM163" t="inlineStr">
@@ -45483,104 +45475,112 @@
       </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>32.02</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
+          <t>86.22</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>97.186</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>0.3284</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>0.0885</t>
+        </is>
+      </c>
+      <c r="AT163" t="inlineStr">
+        <is>
+          <t>0.2584</t>
+        </is>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>69.18</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>4.49</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>33.97</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>18.84</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>0.0612</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>34.49</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
           <t>87.67</t>
         </is>
       </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>98.2909</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>0.3337</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr">
-        <is>
-          <t>0.0818</t>
-        </is>
-      </c>
-      <c r="AT163" t="inlineStr">
-        <is>
-          <t>0.2972</t>
-        </is>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>70.75</t>
-        </is>
-      </c>
-      <c r="AV163" t="inlineStr">
-        <is>
-          <t>12.4</t>
-        </is>
-      </c>
-      <c r="AW163" t="inlineStr">
-        <is>
-          <t>32.18</t>
-        </is>
-      </c>
-      <c r="AX163" t="inlineStr">
-        <is>
-          <t>19.29</t>
-        </is>
-      </c>
-      <c r="AY163" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="AZ163" t="inlineStr">
-        <is>
-          <t>0.0939</t>
-        </is>
-      </c>
-      <c r="BA163" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="BB163" t="inlineStr">
-        <is>
-          <t>40.09</t>
-        </is>
-      </c>
-      <c r="BC163" t="inlineStr">
-        <is>
-          <t>85.32</t>
-        </is>
-      </c>
       <c r="BD163" t="inlineStr">
         <is>
-          <t>0.2785</t>
+          <t>0.274</t>
         </is>
       </c>
       <c r="BE163" t="inlineStr">
         <is>
-          <t>0.0436</t>
+          <t>0.0912</t>
         </is>
       </c>
       <c r="BF163" t="inlineStr">
         <is>
-          <t>6.45</t>
-        </is>
-      </c>
-      <c r="BG163" t="inlineStr"/>
-      <c r="BH163" t="inlineStr"/>
+          <t>23.82</t>
+        </is>
+      </c>
+      <c r="BG163" t="inlineStr">
+        <is>
+          <t>In From RF</t>
+        </is>
+      </c>
+      <c r="BH163" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
       <c r="BI163" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ163" t="inlineStr"/>
@@ -45966,7 +45966,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>74</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>80</v>
       </c>
       <c r="U2" t="n">
-        <v>31.6</v>
+        <v>30.3</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -46066,7 +46066,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 1 HR</t>
+          <t>Last 7 games: 5/25, 1 HR</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -51209,47 +51209,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>650489</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Willi Castro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-02T18:10:00Z</t>
+          <t>2026-07-02T19:10:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Chase Burns</t>
+          <t>Ryan Gusto</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>695505</t>
+          <t>687473</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -51258,7 +51258,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>55.6</v>
+        <v>55.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -51272,26 +51272,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>53.4</v>
+        <v>28.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>37.9</v>
+        <v>50.8</v>
       </c>
       <c r="R21" t="n">
-        <v>47.6</v>
+        <v>81.7</v>
       </c>
       <c r="S21" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U21" t="n">
-        <v>65.2</v>
+        <v>34.2</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -51305,7 +51305,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -51343,27 +51343,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/31, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 9.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.8% barrel, 6.5 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -51373,112 +51373,112 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>12.78</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>45.66</t>
+          <t>40.31</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>91.47</t>
+          <t>87.96</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>102.3936</t>
+          <t>100.1044</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.3687</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.2077</t>
+          <t>0.1316</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3308</t>
+          <t>0.3039</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>74.67</t>
+          <t>72.51</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.2224</t>
+          <t>0.1253</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>38.91</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>89.22</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.3511</t>
+          <t>0.4446</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.1711</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-07-02.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-02.xlsx
@@ -3255,32 +3255,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>678246</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-02T22:40:00Z</t>
+          <t>2026-07-03T02:10:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Slade Cecconi</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>677944</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3318,17 +3318,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Pitcher Vulnerable, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>55.6</v>
+        <v>39.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>47.9</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>58.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -3337,7 +3337,7 @@
         <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>66.90000000000001</v>
+        <v>43.2</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -3399,132 +3399,132 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/28, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.1% barrel, 15.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 12.6% barrel, 13.9 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>90.05</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.5013</t>
+          <t>100.2865</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.5071</t>
+          <t>0.449</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2417</t>
+          <t>0.1819</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3778</t>
+          <t>0.3342</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.12</t>
+          <t>72.88</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>25.42</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>35.31</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2188</t>
+          <t>0.2023</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>91.06</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.4463</t>
+          <t>0.5377</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1842</t>
+          <t>0.242</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -3535,32 +3535,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>678246</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-03T02:10:00Z</t>
+          <t>2026-07-02T22:40:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Slade Cecconi</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>677944</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>60.5</v>
+        <v>60.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3598,17 +3598,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>39.8</v>
+        <v>55.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>70.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="R12" t="n">
-        <v>64.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="S12" t="n">
         <v>100</v>
@@ -3617,7 +3617,7 @@
         <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>43.2</v>
+        <v>60.7</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3669,142 +3669,142 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 12.6% barrel, 13.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.1% barrel, 15.6 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>12.97</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>90.05</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.2865</t>
+          <t>100.5013</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>0.5071</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1819</t>
+          <t>0.2417</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3342</t>
+          <t>0.3778</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>73.12</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>25.42</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.2023</t>
+          <t>0.2188</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>91.06</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.5377</t>
+          <t>0.4463</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>0.1842</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -5227,47 +5227,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>696135</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kahlil Watson</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-02T22:40:00Z</t>
+          <t>2026-07-03T02:10:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>58.9</v>
+        <v>58.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5290,61 +5290,65 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>54.7</v>
+        <v>44.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>40.7</v>
+        <v>57.8</v>
       </c>
       <c r="R18" t="n">
-        <v>58.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>94.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T18" t="n">
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>36</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5361,12 +5365,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5376,127 +5380,127 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Last 7 games: 5/28, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 10.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.2% barrel, 11.6 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>45.49</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>89.84</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>100.2169</t>
+          <t>100.5071</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>0.434</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>0.1899</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.3176</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.98</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>27.95</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>27.89</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.1489</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.4076</t>
+          <t>0.4377</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1468</t>
+          <t>0.1943</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>28.98</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -5507,47 +5511,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>696135</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Kahlil Watson</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-03T02:10:00Z</t>
+          <t>2026-07-02T22:40:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>808963</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -5556,7 +5560,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>58.8</v>
+        <v>58.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5570,65 +5574,61 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>44.6</v>
+        <v>54.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>57.8</v>
+        <v>40.7</v>
       </c>
       <c r="R19" t="n">
-        <v>64.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="S19" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T19" t="n">
         <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -5645,12 +5645,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -5660,127 +5660,127 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Contact streak: 7/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.2% barrel, 11.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 10.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>45.49</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>89.84</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>100.5071</t>
+          <t>100.2169</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>0.454</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1899</t>
+          <t>0.214</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3176</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>72.98</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1489</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.4377</t>
+          <t>0.4076</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1943</t>
+          <t>0.1468</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>28.98</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>
@@ -10275,47 +10275,47 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>803011</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-03T02:10:00Z</t>
+          <t>2026-07-02T22:40:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Slade Cecconi</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>677944</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -10324,7 +10324,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10338,57 +10338,61 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>31.4</v>
+        <v>26.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>69.5</v>
+        <v>47.9</v>
       </c>
       <c r="R36" t="n">
-        <v>64.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="S36" t="n">
-        <v>44.8</v>
+        <v>93.2</v>
       </c>
       <c r="T36" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U36" t="n">
-        <v>50.3</v>
+        <v>58</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y36" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr"/>
@@ -10405,12 +10409,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -10420,12 +10424,12 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Contact streak: 10/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 12.6% barrel, 13.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 15.6 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -10435,112 +10439,112 @@
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>89.35</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>100.1884</t>
+          <t>98.3656</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>0.441</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.1398</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3588</t>
+          <t>0.374</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>70.62</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.1668</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>91.06</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.5377</t>
+          <t>0.4463</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>0.1842</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -10551,47 +10555,47 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-02T22:40:00Z</t>
+          <t>2026-07-03T02:10:00Z</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Slade Cecconi</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>677944</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -10600,7 +10604,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>51.8</v>
+        <v>52.2</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10614,61 +10618,57 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>26.9</v>
+        <v>31.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>47.9</v>
+        <v>69.5</v>
       </c>
       <c r="R37" t="n">
-        <v>58.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S37" t="n">
-        <v>93.2</v>
+        <v>44.8</v>
       </c>
       <c r="T37" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U37" t="n">
-        <v>48.5</v>
+        <v>50.3</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
@@ -10685,12 +10685,12 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -10700,12 +10700,12 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Contact streak: 9/28 over last 7 games</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 15.6 HR allowed</t>
+          <t>switch hitter; pitcher baseline 12.6% barrel, 13.9 HR allowed</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -10715,112 +10715,112 @@
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>38.22</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>89.35</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>98.3656</t>
+          <t>100.1884</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>0.446</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.1398</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>0.3588</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>70.62</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1668</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>91.06</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>0.4463</t>
+          <t>0.5377</t>
         </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>0.1842</t>
+          <t>0.242</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr"/>
@@ -11951,47 +11951,47 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>687263</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-03T01:40:00Z</t>
+          <t>2026-07-02T22:40:00Z</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Bryce Miller</t>
+          <t>Slade Cecconi</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>682243</t>
+          <t>677944</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -12014,26 +12014,26 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>50.8</v>
+        <v>23.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>35.9</v>
+        <v>47.9</v>
       </c>
       <c r="R42" t="n">
-        <v>38.9</v>
+        <v>58.6</v>
       </c>
       <c r="S42" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T42" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U42" t="n">
-        <v>36.3</v>
+        <v>39.5</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -12100,127 +12100,127 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 6/23, 1 HR</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 15.6 HR allowed</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>100.1597</t>
+          <t>98.2797</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>0.4362</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>0.2202</t>
+          <t>0.1202</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>0.3223</t>
+          <t>0.3027</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>70.98</t>
+          <t>71.95</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>11.55</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>32.14</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>23.92</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>0.2233</t>
+          <t>0.1219</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>34.11</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>87.92</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="BD42" t="inlineStr">
         <is>
-          <t>0.3755</t>
+          <t>0.4463</t>
         </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.1842</t>
         </is>
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BG42" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI42" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ42" t="inlineStr"/>
@@ -12231,47 +12231,47 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>687263</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-02T22:40:00Z</t>
+          <t>2026-07-03T01:40:00Z</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Slade Cecconi</t>
+          <t>Bryce Miller</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>677944</t>
+          <t>682243</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -12280,7 +12280,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -12294,26 +12294,26 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>23.2</v>
+        <v>50.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>47.9</v>
+        <v>35.9</v>
       </c>
       <c r="R43" t="n">
-        <v>58.6</v>
+        <v>38.9</v>
       </c>
       <c r="S43" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T43" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U43" t="n">
-        <v>34.9</v>
+        <v>36.3</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -12380,127 +12380,127 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 15.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>98.2797</t>
+          <t>100.1597</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.4362</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>0.1202</t>
+          <t>0.2202</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>0.3027</t>
+          <t>0.3223</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>71.95</t>
+          <t>70.98</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>11.55</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>23.92</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>0.1219</t>
+          <t>0.2233</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>34.11</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>87.92</t>
         </is>
       </c>
       <c r="BD43" t="inlineStr">
         <is>
-          <t>0.4463</t>
+          <t>0.3755</t>
         </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
-          <t>0.1842</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="BG43" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr"/>
@@ -21763,47 +21763,47 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>671056</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Iván Herrera</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-02T23:15:00Z</t>
+          <t>2026-07-02T22:40:00Z</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Hurston Waldrep</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>694462</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -21826,26 +21826,26 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>37.3</v>
+        <v>12.8</v>
       </c>
       <c r="Q77" t="n">
-        <v>9.699999999999999</v>
+        <v>39.6</v>
       </c>
       <c r="R77" t="n">
-        <v>61.9</v>
+        <v>58.6</v>
       </c>
       <c r="S77" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T77" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -21897,12 +21897,12 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -21912,12 +21912,12 @@
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/24, 0 HR</t>
+          <t>Last 7 games: 6/22, 0 HR</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.3% barrel, 0.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.3% barrel, 10.2 HR allowed</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
@@ -21927,97 +21927,97 @@
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>43.15</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>89.94</t>
+          <t>86.81</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>101.3798</t>
+          <t>97.4049</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>0.4294</t>
+          <t>0.3538</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>0.3633</t>
+          <t>0.3027</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>74.26</t>
+          <t>69.93</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>45.18</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>43.57</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.1604</t>
+          <t>0.1112</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>40.09</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>85.32</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BD77" t="inlineStr">
         <is>
-          <t>0.2785</t>
+          <t>0.4076</t>
         </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
-          <t>0.0436</t>
+          <t>0.1468</t>
         </is>
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="BG77" t="inlineStr">
@@ -22027,12 +22027,12 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI77" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ77" t="inlineStr"/>
@@ -22043,47 +22043,47 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>671056</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Iván Herrera</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-02T22:40:00Z</t>
+          <t>2026-07-02T23:15:00Z</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Hurston Waldrep</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>694462</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -22092,7 +22092,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -22106,26 +22106,26 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>12.8</v>
+        <v>37.3</v>
       </c>
       <c r="Q78" t="n">
-        <v>39.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R78" t="n">
-        <v>58.6</v>
+        <v>61.9</v>
       </c>
       <c r="S78" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T78" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U78" t="n">
-        <v>20.9</v>
+        <v>0</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
@@ -22177,12 +22177,12 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -22192,12 +22192,12 @@
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 2/24, 0 HR</t>
         </is>
       </c>
       <c r="AL78" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.3% barrel, 10.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.3% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
@@ -22207,97 +22207,97 @@
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>43.15</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>86.81</t>
+          <t>89.94</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>97.4049</t>
+          <t>101.3798</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>0.3538</t>
+          <t>0.4294</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr">
         <is>
-          <t>0.3027</t>
+          <t>0.3633</t>
         </is>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>69.93</t>
+          <t>74.26</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>45.18</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>43.57</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>0.1112</t>
+          <t>0.1604</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>40.09</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>85.32</t>
         </is>
       </c>
       <c r="BD78" t="inlineStr">
         <is>
-          <t>0.4076</t>
+          <t>0.2785</t>
         </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
-          <t>0.1468</t>
+          <t>0.0436</t>
         </is>
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BG78" t="inlineStr">
@@ -22307,12 +22307,12 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>95</t>
         </is>
       </c>
       <c r="BI78" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ78" t="inlineStr"/>
@@ -23862,7 +23862,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -23872,7 +23872,7 @@
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/15, 0 HR</t>
+          <t>Last 7 games: 1/14, 0 HR</t>
         </is>
       </c>
       <c r="AL84" t="inlineStr">
@@ -33849,32 +33849,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>678246</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-02T22:40:00Z</t>
+          <t>2026-07-03T02:10:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -33884,12 +33884,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Slade Cecconi</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>677944</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -33912,17 +33912,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Pitcher Vulnerable, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>55.6</v>
+        <v>39.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>47.9</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>58.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -33931,7 +33931,7 @@
         <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>66.90000000000001</v>
+        <v>43.2</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -33983,7 +33983,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -33993,132 +33993,132 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/28, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.1% barrel, 15.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 12.6% barrel, 13.9 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>90.05</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.5013</t>
+          <t>100.2865</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.5071</t>
+          <t>0.449</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2417</t>
+          <t>0.1819</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3778</t>
+          <t>0.3342</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.12</t>
+          <t>72.88</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>25.42</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>35.31</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2188</t>
+          <t>0.2023</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>91.06</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.4463</t>
+          <t>0.5377</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1842</t>
+          <t>0.242</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -34129,32 +34129,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>678246</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-03T02:10:00Z</t>
+          <t>2026-07-02T22:40:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -34164,12 +34164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Slade Cecconi</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>677944</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -34178,7 +34178,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>60.5</v>
+        <v>60.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -34192,17 +34192,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>39.8</v>
+        <v>55.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>70.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="R12" t="n">
-        <v>64.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="S12" t="n">
         <v>100</v>
@@ -34211,7 +34211,7 @@
         <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>43.2</v>
+        <v>60.7</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -34263,142 +34263,142 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 12.6% barrel, 13.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.1% barrel, 15.6 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>12.97</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>90.05</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.2865</t>
+          <t>100.5013</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>0.5071</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1819</t>
+          <t>0.2417</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3342</t>
+          <t>0.3778</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>73.12</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>25.42</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.2023</t>
+          <t>0.2188</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>91.06</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.5377</t>
+          <t>0.4463</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>0.1842</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -35821,47 +35821,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>696135</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kahlil Watson</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-02T22:40:00Z</t>
+          <t>2026-07-03T02:10:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -35870,7 +35870,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>58.9</v>
+        <v>58.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -35884,61 +35884,65 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>54.7</v>
+        <v>44.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>40.7</v>
+        <v>57.8</v>
       </c>
       <c r="R18" t="n">
-        <v>58.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>94.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T18" t="n">
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>36</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -35955,12 +35959,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -35970,127 +35974,127 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Last 7 games: 5/28, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 10.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.2% barrel, 11.6 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>45.49</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>89.84</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>100.2169</t>
+          <t>100.5071</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>0.434</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>0.1899</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.3176</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.98</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>27.95</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>27.89</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.1489</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.4076</t>
+          <t>0.4377</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1468</t>
+          <t>0.1943</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>28.98</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -36101,47 +36105,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>696135</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Kahlil Watson</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-03T02:10:00Z</t>
+          <t>2026-07-02T22:40:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>808963</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -36150,7 +36154,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>58.8</v>
+        <v>58.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -36164,65 +36168,61 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>44.6</v>
+        <v>54.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>57.8</v>
+        <v>40.7</v>
       </c>
       <c r="R19" t="n">
-        <v>64.59999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="S19" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T19" t="n">
         <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -36239,12 +36239,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -36254,127 +36254,127 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Contact streak: 7/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.2% barrel, 11.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 10.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>45.49</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>89.84</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>100.5071</t>
+          <t>100.2169</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>0.454</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1899</t>
+          <t>0.214</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3176</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>72.98</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1489</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.4377</t>
+          <t>0.4076</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1943</t>
+          <t>0.1468</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>28.98</t>
+          <t>22.01</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>
